--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGluzman\Documents\Agentic-AI\Side Quests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90CB1F52-EDCB-4EA4-BA04-6C5FA0438897}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DDC137-7A65-4838-BAA9-79EF761C186E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -166,27 +166,6 @@
   </si>
   <si>
     <t>While teachers are struggling to adjust to the proliferation and misuse of AI tools, students are either too scared to use Gen AI or not using this technology ethically, effectively, or responsibly. The Student AI Micro-Course on Brightspace aims to remedy this situation – helping students become AI literate and transparent with any AI usage.</t>
-  </si>
-  <si>
-    <t>Dermot Foley - Lehman College</t>
-  </si>
-  <si>
-    <t>dermot.foley@lehman.cuny.edu</t>
-  </si>
-  <si>
-    <t>Unsure - Presenting with Kenny Hirschmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reimagining Adult Learning through Collaborative Open Pedagogy Planning, Design, and Execution. </t>
-  </si>
-  <si>
-    <t>Victoria Smith &amp; Stacy Katz - Lehman AND Richard Knipel The Office of Library Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:35 am - 11:05 am </t>
-  </si>
-  <si>
-    <t>Our presentation details the strategic design of a Wikimedia initiative at Lehman College that conceptually resituates students from passive consumers into active knowledge producers.</t>
   </si>
 </sst>
 </file>
@@ -300,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q6" totalsRowShown="0" headerRowDxfId="15">
-  <autoFilter ref="A1:Q6" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q5" totalsRowShown="0" headerRowDxfId="15">
+  <autoFilter ref="A1:Q5" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{D19C9C43-3E8A-4B96-8511-DA0AA1218075}" name="Id" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{DFE20693-241D-4E42-8AD2-BF39A0DEA3B4}" name="Start time"/>
@@ -622,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="17" width="20" bestFit="1" customWidth="1"/>
@@ -844,51 +823,6 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46139.513680555603</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46139.518726851798</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGluzman\Documents\Agentic-AI\Side Quests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DDC137-7A65-4838-BAA9-79EF761C186E}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7144937A-E03B-4E14-8AFD-554FFB2F75B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,10 +141,10 @@
     <t>upLIFTing CUNY: AI Perspectives from the Field</t>
   </si>
   <si>
-    <t>Dermot Foley - Lehman; Mariya Gluzman - Brooklyn; Lisette Jolalpa - City Tech; Stephen Zweibel - GC - All LIFT.  We will have one more hopefully by the end of today.</t>
-  </si>
-  <si>
-    <t>Bronx EdTech Showcase - time unknown</t>
+    <t xml:space="preserve">Dermot Foley - Lehman (lift); Mariya Gluzman - Brooklyn (lift); Lisette Jolalpa - City Tech (lift); Stephen Zweibel - GC (lift) </t>
+  </si>
+  <si>
+    <t>11:35 AM – 12:15 PM in Room NL 137</t>
   </si>
   <si>
     <t>As AI continues to reshape higher education, instructional designers, educational technologists, and online learning professionals are navigating its impact in real time. This panel brings together members of the LIFT@CUNY Collective—a grassroots, cross-campus community of practice—to share perspectives from the field on how AI is changing their work supporting campus communities. Panelists will discuss AI initiatives and programs on their respective campuses while reflecting on emerging practices, obstacles, and lessons learned. Attendees will gain practical insights from diverse institutional and philosophical contexts and explore how we can collectively support thoughtful, equitable, and effective uses of AI in teaching and learning.</t>
@@ -767,7 +767,7 @@
       <c r="J4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" t="s">
         <v>35</v>
       </c>
       <c r="L4" s="4" t="s">

--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGluzman\Documents\Agentic-AI\Side Quests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7144937A-E03B-4E14-8AFD-554FFB2F75B1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28AE8EE3-BF77-42F5-A632-6D1DCAFF7906}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -141,10 +141,10 @@
     <t>upLIFTing CUNY: AI Perspectives from the Field</t>
   </si>
   <si>
-    <t xml:space="preserve">Dermot Foley - Lehman (lift); Mariya Gluzman - Brooklyn (lift); Lisette Jolalpa - City Tech (lift); Stephen Zweibel - GC (lift) </t>
-  </si>
-  <si>
-    <t>11:35 AM – 12:15 PM in Room NL 137</t>
+    <t>Dermot Foley - Lehman; Mariya Gluzman - Brooklyn; Lisette Jolalpa - City Tech; Stephen Zweibel - GC - All LIFT.  We will have one more hopefully by the end of today.</t>
+  </si>
+  <si>
+    <t>Bronx EdTech Showcase - time unknown</t>
   </si>
   <si>
     <t>As AI continues to reshape higher education, instructional designers, educational technologists, and online learning professionals are navigating its impact in real time. This panel brings together members of the LIFT@CUNY Collective—a grassroots, cross-campus community of practice—to share perspectives from the field on how AI is changing their work supporting campus communities. Panelists will discuss AI initiatives and programs on their respective campuses while reflecting on emerging practices, obstacles, and lessons learned. Attendees will gain practical insights from diverse institutional and philosophical contexts and explore how we can collectively support thoughtful, equitable, and effective uses of AI in teaching and learning.</t>
@@ -166,6 +166,57 @@
   </si>
   <si>
     <t>While teachers are struggling to adjust to the proliferation and misuse of AI tools, students are either too scared to use Gen AI or not using this technology ethically, effectively, or responsibly. The Student AI Micro-Course on Brightspace aims to remedy this situation – helping students become AI literate and transparent with any AI usage.</t>
+  </si>
+  <si>
+    <t>Dermot Foley - Lehman College</t>
+  </si>
+  <si>
+    <t>dermot.foley@lehman.cuny.edu</t>
+  </si>
+  <si>
+    <t>Unsure - Presenting with Kenny Hirschmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reimagining Adult Learning through Collaborative Open Pedagogy Planning, Design, and Execution. </t>
+  </si>
+  <si>
+    <t>Victoria Smith &amp; Stacy Katz - Lehman AND Richard Knipel The Office of Library Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:35 am - 11:05 am </t>
+  </si>
+  <si>
+    <t>Our presentation details the strategic design of a Wikimedia initiative at Lehman College that conceptually resituates students from passive consumers into active knowledge producers.</t>
+  </si>
+  <si>
+    <t>Don’t AI Alone: Building AI Community and Sharing Practices</t>
+  </si>
+  <si>
+    <t>Edgar Troudt - Hunter College; Kenny Hirschmann - Hunter College (LIFT); Christina Katopodis - Hunter College; LaRoi Lawton - Bronx Community College</t>
+  </si>
+  <si>
+    <t>12:20 PM - NL 136</t>
+  </si>
+  <si>
+    <t>This session explores how educators and academic support professionals can build meaningful, supportive communities around the use of AI in teaching and learning. Drawing on examples from across CUNY—including grassroots networks, campus-based working groups, and system-wide initiatives—panelists will share how these communities create space for collaboration, experimentation, and critical dialogue. The conversation will also highlight how community-building translates into practice, offering concrete approaches for integrating AI into teaching while maintaining a focus on equity, access, and student learning.</t>
+  </si>
+  <si>
+    <t>Jean Kelly Queens College</t>
+  </si>
+  <si>
+    <t>jean.kelly@qc.cuny.edu</t>
+  </si>
+  <si>
+    <t>Technology-Informed Inclusive Teaching: A Model for Engaging Faculty and Other Adult Learners through UDL​</t>
+  </si>
+  <si>
+    <t>[please list us in this order] Elena Sigman (Queens College), Sally Izquierdo (Queens College), Jean Kelly (Queens College) &amp; Melissa Lovitz (Queens College)</t>
+  </si>
+  <si>
+    <t>1:55 PM – 2:55 PM, Room C197</t>
+  </si>
+  <si>
+    <t>This session examines how Universal Design for Learning (UDL) and accessible course technology can advance learner agency and inclusion for adult and nontraditional students. The methodology draws on faculty development workshops at Queens College that integrate UDL principles directly into Brightspace, treating technology as part of the learning pathway rather than an add-on.</t>
   </si>
 </sst>
 </file>
@@ -181,15 +232,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -197,20 +254,106 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -279,8 +422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q5" totalsRowShown="0" headerRowDxfId="15">
-  <autoFilter ref="A1:Q5" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q8" totalsRowShown="0" headerRowDxfId="15">
+  <autoFilter ref="A1:Q8" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{D19C9C43-3E8A-4B96-8511-DA0AA1218075}" name="Id" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{DFE20693-241D-4E42-8AD2-BF39A0DEA3B4}" name="Start time"/>
@@ -601,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="17" width="20" bestFit="1" customWidth="1"/>
@@ -661,168 +804,305 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>46127.992812500001</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>46128.001782407409</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M2" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="409.6">
-      <c r="A3" s="3">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <v>46128.742488425902</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <v>46128.746898148202</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>46136.515277777798</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>46136.5167476852</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="11"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="3">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>46136.610393518502</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <v>46136.622662037</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="12"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46139.513680555603</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46139.518726851798</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46142.674340277801</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46142.676585648202</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="12"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14">
+        <v>46142.684398148202</v>
+      </c>
+      <c r="C8" s="14">
+        <v>46142.692418981504</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q8" s="16" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGluzman\Documents\Agentic-AI\Side Quests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28AE8EE3-BF77-42F5-A632-6D1DCAFF7906}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55ACBBB1-1C96-4A27-974F-35553DA813DE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -166,27 +166,6 @@
   </si>
   <si>
     <t>While teachers are struggling to adjust to the proliferation and misuse of AI tools, students are either too scared to use Gen AI or not using this technology ethically, effectively, or responsibly. The Student AI Micro-Course on Brightspace aims to remedy this situation – helping students become AI literate and transparent with any AI usage.</t>
-  </si>
-  <si>
-    <t>Dermot Foley - Lehman College</t>
-  </si>
-  <si>
-    <t>dermot.foley@lehman.cuny.edu</t>
-  </si>
-  <si>
-    <t>Unsure - Presenting with Kenny Hirschmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reimagining Adult Learning through Collaborative Open Pedagogy Planning, Design, and Execution. </t>
-  </si>
-  <si>
-    <t>Victoria Smith &amp; Stacy Katz - Lehman AND Richard Knipel The Office of Library Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:35 am - 11:05 am </t>
-  </si>
-  <si>
-    <t>Our presentation details the strategic design of a Wikimedia initiative at Lehman College that conceptually resituates students from passive consumers into active knowledge producers.</t>
   </si>
   <si>
     <t>Don’t AI Alone: Building AI Community and Sharing Practices</t>
@@ -326,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -336,7 +315,6 @@
     </xf>
     <xf numFmtId="22" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -346,14 +324,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,6 +345,7 @@
   <dxfs count="16">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -422,8 +407,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q8" totalsRowShown="0" headerRowDxfId="15">
-  <autoFilter ref="A1:Q8" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q7" totalsRowShown="0" headerRowDxfId="15">
+  <autoFilter ref="A1:Q7" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{D19C9C43-3E8A-4B96-8511-DA0AA1218075}" name="Id" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{DFE20693-241D-4E42-8AD2-BF39A0DEA3B4}" name="Start time"/>
@@ -744,10 +729,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="17" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="134.25" customHeight="1">
@@ -803,7 +789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" ht="231">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -840,50 +826,50 @@
       <c r="P2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="409.6">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>46128.742488425902</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>46128.746898148202</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -897,211 +883,166 @@
       <c r="C4" s="3">
         <v>46136.5167476852</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="11"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>46136.610393518502</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>46136.622662037</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="12"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="8"/>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46139.513680555603</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46139.518726851798</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46142.674340277801</v>
+      </c>
+      <c r="C6" s="6">
+        <v>46142.676585648202</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="J6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="K6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7" spans="1:17" ht="366">
+      <c r="A7" s="10">
+        <v>7</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46142.684398148202</v>
+      </c>
+      <c r="C7" s="11">
+        <v>46142.692418981504</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="P6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7">
-        <v>46142.674340277801</v>
-      </c>
-      <c r="C7" s="7">
-        <v>46142.676585648202</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="O7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="P7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="Q7" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="12"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="13">
-        <v>7</v>
-      </c>
-      <c r="B8" s="14">
-        <v>46142.684398148202</v>
-      </c>
-      <c r="C8" s="14">
-        <v>46142.692418981504</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/sessions.xlsx
+++ b/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGluzman\Documents\Agentic-AI\Side Quests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55ACBBB1-1C96-4A27-974F-35553DA813DE}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{DF3FAF12-CC28-4D32-B632-7FB7516983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E102D5-47C2-4B89-8B79-1FABF8A3F0AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,10 +141,10 @@
     <t>upLIFTing CUNY: AI Perspectives from the Field</t>
   </si>
   <si>
-    <t>Dermot Foley - Lehman; Mariya Gluzman - Brooklyn; Lisette Jolalpa - City Tech; Stephen Zweibel - GC - All LIFT.  We will have one more hopefully by the end of today.</t>
-  </si>
-  <si>
-    <t>Bronx EdTech Showcase - time unknown</t>
+    <t>Dermot Foley - Lehman (LIFT); Mariya Gluzman - Brooklyn (LIFT); Lisette Jolalpa - City Tech (LIFT); Stephen Zweibel - GC (LIFT)</t>
+  </si>
+  <si>
+    <t>11:35 AM – 12:15 PM in Room NL 137</t>
   </si>
   <si>
     <t>As AI continues to reshape higher education, instructional designers, educational technologists, and online learning professionals are navigating its impact in real time. This panel brings together members of the LIFT@CUNY Collective—a grassroots, cross-campus community of practice—to share perspectives from the field on how AI is changing their work supporting campus communities. Panelists will discuss AI initiatives and programs on their respective campuses while reflecting on emerging practices, obstacles, and lessons learned. Attendees will gain practical insights from diverse institutional and philosophical contexts and explore how we can collectively support thoughtful, equitable, and effective uses of AI in teaching and learning.</t>
@@ -313,22 +313,15 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -336,58 +329,101 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
@@ -407,12 +443,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q7" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}" name="OfficeForms.Table3" displayName="OfficeForms.Table3" ref="A1:Q7" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:Q7" xr:uid="{D9B9F385-DB1F-4416-A300-E805DC96370A}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{D19C9C43-3E8A-4B96-8511-DA0AA1218075}" name="Id" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{DFE20693-241D-4E42-8AD2-BF39A0DEA3B4}" name="Start time"/>
-    <tableColumn id="3" xr3:uid="{1393CB30-7BC0-4A0F-BBE8-818AACCD4C4F}" name="Completion time"/>
+    <tableColumn id="1" xr3:uid="{D19C9C43-3E8A-4B96-8511-DA0AA1218075}" name="Id" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{DFE20693-241D-4E42-8AD2-BF39A0DEA3B4}" name="Start time" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{1393CB30-7BC0-4A0F-BBE8-818AACCD4C4F}" name="Completion time" dataDxfId="14"/>
     <tableColumn id="4" xr3:uid="{4F4922CB-2B34-4038-9301-E54C3EFB4164}" name="Email" dataDxfId="13"/>
     <tableColumn id="5" xr3:uid="{F36DDCAB-1A35-4935-BB4C-B646F94A7629}" name="Name" dataDxfId="12"/>
     <tableColumn id="6" xr3:uid="{A5FD2E9A-3A3F-4886-A114-EAF0B0B5C8F2}" name="Please provide your full name and campus affiliation." dataDxfId="11"/>
@@ -793,255 +829,255 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="9">
         <v>46127.992812500001</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="9">
         <v>46128.001782407409</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="10"/>
+      <c r="P2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="Q2" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="409.6">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="11">
         <v>46128.742488425902</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="11">
         <v>46128.746898148202</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" ht="409.6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="9">
         <v>46136.515277777798</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="9">
         <v>46136.5167476852</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="14"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="7"/>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="5">
+    <row r="5" spans="1:17" ht="275.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="11">
         <v>46136.610393518502</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="11">
         <v>46136.622662037</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="8"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="5">
+    <row r="6" spans="1:17" ht="409.6">
+      <c r="A6" s="3">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="11">
         <v>46142.674340277801</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="11">
         <v>46142.676585648202</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" ht="366">
-      <c r="A7" s="10">
+      <c r="A7" s="5">
         <v>7</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="14">
         <v>46142.684398148202</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="14">
         <v>46142.692418981504</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12" t="s">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="8" t="s">
         <v>52</v>
       </c>
     </row>
